--- a/data/b2_bonsucesso/B2 Bonsucesso 10-2025.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 10-2025.xlsx
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>64609.44</v>
+        <v>64526.71</v>
       </c>
     </row>
     <row r="3">
@@ -4801,43 +4801,43 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2862.58</v>
+        <v>2848.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3701.75</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>45940</v>
+        <v>45941</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3600</v>
+        <v>3749.98</v>
       </c>
     </row>
     <row r="6">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3966.7</v>
+        <v>3629.4</v>
       </c>
     </row>
     <row r="7">
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1491.49</v>
+        <v>1397.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>45945</v>
+        <v>45944</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>10757.57</v>
+        <v>1815.38</v>
       </c>
     </row>
     <row r="9">
@@ -4900,106 +4900,106 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2153.21</v>
+        <v>10305.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>45949</v>
+        <v>45945</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3745</v>
+        <v>1860.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>45950</v>
+        <v>45947</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>23129.54</v>
+        <v>1346.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>45951</v>
+        <v>45949</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1269.79</v>
+        <v>2044.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>45952</v>
+        <v>45949</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2345.73</v>
+        <v>3604.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45953</v>
+        <v>45950</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1227.64</v>
+        <v>22818.65</v>
       </c>
     </row>
     <row r="15">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1334.95</v>
+        <v>1494.17</v>
       </c>
     </row>
     <row r="16">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3638.05</v>
+        <v>3505.14</v>
       </c>
     </row>
     <row r="17">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2692.75</v>
+        <v>2649.02</v>
       </c>
     </row>
   </sheetData>
